--- a/data/dividends_info_20260525.xlsx
+++ b/data/dividends_info_20260525.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>57.34000015258789</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1569584927807819</v>
+        <v>0.1551189232849395</v>
       </c>
       <c r="J2" t="n">
         <v>294</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.75</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.255605381165919</v>
+        <v>1.256732478297831</v>
       </c>
       <c r="J3" t="n">
         <v>273</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>203</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>57.34000015258789</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1569584927807819</v>
+        <v>0.1551189232849395</v>
       </c>
       <c r="J6" t="n">
         <v>203</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>182</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.86000061035156</v>
+        <v>23.04000091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>1.181102330669831</v>
+        <v>1.171874953433873</v>
       </c>
       <c r="J8" t="n">
         <v>182</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.78000020980835</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>3.460207486854598</v>
+        <v>3.44827574867131</v>
       </c>
       <c r="J9" t="n">
         <v>175</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.949999809265137</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8633093762105317</v>
+        <v>0.8450704338862249</v>
       </c>
       <c r="J10" t="n">
         <v>147</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.199999809265137</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9615384968074835</v>
+        <v>0.9541985149615856</v>
       </c>
       <c r="J12" t="n">
         <v>133</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.960000038146973</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J13" t="n">
         <v>126</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.85000038146973</v>
+        <v>23.04000091552734</v>
       </c>
       <c r="I14" t="n">
-        <v>1.181619236290942</v>
+        <v>1.171874953433873</v>
       </c>
       <c r="J14" t="n">
         <v>119</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>57.34000015258789</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1569584927807819</v>
+        <v>0.1551189232849395</v>
       </c>
       <c r="J15" t="n">
         <v>119</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.559999942779541</v>
+        <v>4.769999980926514</v>
       </c>
       <c r="I16" t="n">
-        <v>6.578947450975963</v>
+        <v>6.289308201249273</v>
       </c>
       <c r="J16" t="n">
         <v>112</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.960000038146973</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J18" t="n">
         <v>70</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I19" t="n">
-        <v>4.295532519351027</v>
+        <v>4.288164721639967</v>
       </c>
       <c r="J19" t="n">
         <v>63</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.795000076293945</v>
+        <v>9.798999786376953</v>
       </c>
       <c r="I20" t="n">
-        <v>2.654415497446061</v>
+        <v>2.653332030494221</v>
       </c>
       <c r="J20" t="n">
         <v>56</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14.65999984741211</v>
+        <v>14.64000034332275</v>
       </c>
       <c r="I21" t="n">
-        <v>4.092769483254234</v>
+        <v>4.098360559627019</v>
       </c>
       <c r="J21" t="n">
         <v>56</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.631999969482422</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I22" t="n">
-        <v>6.057268773362658</v>
+        <v>6.077348258424673</v>
       </c>
       <c r="J22" t="n">
         <v>56</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.179999828338623</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I24" t="n">
-        <v>1.618123022292755</v>
+        <v>1.633986958659309</v>
       </c>
       <c r="J24" t="n">
         <v>56</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.434999942779541</v>
+        <v>4.355000019073486</v>
       </c>
       <c r="I26" t="n">
-        <v>2.705749753060708</v>
+        <v>2.755453489654167</v>
       </c>
       <c r="J26" t="n">
         <v>49</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.640000104904175</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I28" t="n">
-        <v>5.681817956043021</v>
+        <v>5.597014785954832</v>
       </c>
       <c r="J28" t="n">
         <v>49</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.220000028610229</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I29" t="n">
-        <v>3.828828779484834</v>
+        <v>3.935185028814982</v>
       </c>
       <c r="J29" t="n">
         <v>42</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31.85000038146973</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4709576081740637</v>
+        <v>0.4731861084854148</v>
       </c>
       <c r="J31" t="n">
         <v>42</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.599999904632568</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7142857264499277</v>
+        <v>0.7017544094471985</v>
       </c>
       <c r="J32" t="n">
         <v>35</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.47999954223633</v>
+        <v>23.23999977111816</v>
       </c>
       <c r="I33" t="n">
-        <v>4.045996671725311</v>
+        <v>4.087779730448301</v>
       </c>
       <c r="J33" t="n">
         <v>28</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.825000047683716</v>
+        <v>1.845000028610229</v>
       </c>
       <c r="I35" t="n">
-        <v>1.808219130836928</v>
+        <v>1.788617858442944</v>
       </c>
       <c r="J35" t="n">
         <v>28</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.295000076293945</v>
+        <v>5.255000114440918</v>
       </c>
       <c r="I36" t="n">
-        <v>5.476864888035575</v>
+        <v>5.518553638144938</v>
       </c>
       <c r="J36" t="n">
         <v>28</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.940000057220459</v>
+        <v>3.921999931335449</v>
       </c>
       <c r="I37" t="n">
-        <v>4.060913646607274</v>
+        <v>4.079551320785455</v>
       </c>
       <c r="J37" t="n">
         <v>28</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.766000032424927</v>
+        <v>2.747999906539917</v>
       </c>
       <c r="I38" t="n">
-        <v>5.010845928244283</v>
+        <v>5.043668293807007</v>
       </c>
       <c r="J38" t="n">
         <v>28</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>51.97000122070312</v>
+        <v>52.02000045776367</v>
       </c>
       <c r="I39" t="n">
-        <v>1.212237801043247</v>
+        <v>1.211072653702709</v>
       </c>
       <c r="J39" t="n">
         <v>28</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.20000076293945</v>
+        <v>19.25</v>
       </c>
       <c r="I41" t="n">
-        <v>4.06249983857076</v>
+        <v>4.051948051948052</v>
       </c>
       <c r="J41" t="n">
         <v>28</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>25.19000053405762</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="I42" t="n">
-        <v>3.374354831198893</v>
+        <v>3.353057148753854</v>
       </c>
       <c r="J42" t="n">
         <v>28</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>57.34000015258789</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1569584927807819</v>
+        <v>0.1551189232849395</v>
       </c>
       <c r="J43" t="n">
         <v>28</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.394000053405762</v>
+        <v>6.355999946594238</v>
       </c>
       <c r="I45" t="n">
-        <v>2.835470730148502</v>
+        <v>2.852422931456233</v>
       </c>
       <c r="J45" t="n">
         <v>28</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.829999923706055</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I46" t="n">
-        <v>2.944507386709863</v>
+        <v>2.921348439820898</v>
       </c>
       <c r="J46" t="n">
         <v>28</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10.02999973297119</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="I47" t="n">
-        <v>2.761714928958868</v>
+        <v>2.753479010397041</v>
       </c>
       <c r="J47" t="n">
         <v>28</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.032000064849854</v>
+        <v>2.992000102996826</v>
       </c>
       <c r="I49" t="n">
-        <v>3.627968260134166</v>
+        <v>3.676470461676207</v>
       </c>
       <c r="J49" t="n">
         <v>21</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.039999961853027</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I50" t="n">
-        <v>1.176470610234702</v>
+        <v>1.142857194757788</v>
       </c>
       <c r="J50" t="n">
         <v>21</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.25</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I51" t="n">
-        <v>4.923076923076923</v>
+        <v>4.848484918543569</v>
       </c>
       <c r="J51" t="n">
         <v>14</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8849999904632568</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="I52" t="n">
-        <v>2.824858787502772</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J52" t="n">
         <v>14</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28.85000038146973</v>
+        <v>28.75</v>
       </c>
       <c r="I53" t="n">
-        <v>3.847486950859627</v>
+        <v>3.860869565217392</v>
       </c>
       <c r="J53" t="n">
         <v>10</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8980000019073486</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I54" t="n">
-        <v>3.340757231211593</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J54" t="n">
         <v>7</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5149999856948853</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="I55" t="n">
-        <v>4.466019541528004</v>
+        <v>4.423077085314424</v>
       </c>
       <c r="J55" t="n">
         <v>7</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2.970296917516995</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.319999933242798</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="I58" t="n">
-        <v>7.75862091290682</v>
+        <v>7.725322141371375</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3201,8 +3201,12 @@
           <t>IT0005600249</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>8.300000190734863</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.614457748264686</v>
+      </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
@@ -3245,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15.10000038146973</v>
+        <v>15.06999969482422</v>
       </c>
       <c r="I60" t="n">
-        <v>1.655629097246862</v>
+        <v>1.658925050183394</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3292,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.470000028610229</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8645533069927757</v>
+        <v>0.862068960792339</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3339,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.070000171661377</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="I62" t="n">
-        <v>3.68550353005931</v>
+        <v>3.667481525766927</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3386,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.69999980926514</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="I63" t="n">
-        <v>4.233576701276691</v>
+        <v>4.202898492634835</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3433,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.309999942779541</v>
+        <v>2.309000015258789</v>
       </c>
       <c r="I64" t="n">
-        <v>4.502164613686547</v>
+        <v>4.504114305445071</v>
       </c>
       <c r="J64" t="n">
         <v>-7</v>
@@ -3480,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.8100004196167</v>
+        <v>10.75500011444092</v>
       </c>
       <c r="I65" t="n">
-        <v>2.682701098454563</v>
+        <v>2.696420240950181</v>
       </c>
       <c r="J65" t="n">
         <v>-7</v>
@@ -3527,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.065000057220459</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I66" t="n">
-        <v>3.728813455997861</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J66" t="n">
         <v>-7</v>
@@ -3574,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>38.96500015258789</v>
+        <v>39.11999893188477</v>
       </c>
       <c r="I67" t="n">
-        <v>4.208905411465983</v>
+        <v>4.192229153317582</v>
       </c>
       <c r="J67" t="n">
         <v>-7</v>
@@ -3621,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>35.11000061035156</v>
+        <v>35.2599983215332</v>
       </c>
       <c r="I68" t="n">
-        <v>5.696382697898146</v>
+        <v>5.672150014762209</v>
       </c>
       <c r="J68" t="n">
         <v>-7</v>
@@ -3668,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.289999961853027</v>
+        <v>3.25</v>
       </c>
       <c r="I69" t="n">
-        <v>3.039513713054178</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="J69" t="n">
         <v>-7</v>
@@ -3715,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>37.75</v>
+        <v>38.68999862670898</v>
       </c>
       <c r="I70" t="n">
-        <v>0.393271523178808</v>
+        <v>0.383716736287277</v>
       </c>
       <c r="J70" t="n">
         <v>-7</v>
@@ -3762,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.57999992370605</v>
+        <v>19.52000045776367</v>
       </c>
       <c r="I71" t="n">
-        <v>4.698672132710942</v>
+        <v>4.713114643571073</v>
       </c>
       <c r="J71" t="n">
         <v>-7</v>
@@ -3809,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>11.10999965667725</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="I72" t="n">
-        <v>2.70027011044682</v>
+        <v>2.70758124608051</v>
       </c>
       <c r="J72" t="n">
         <v>-7</v>
@@ -3856,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>83.76000213623047</v>
+        <v>83.98000335693359</v>
       </c>
       <c r="I73" t="n">
-        <v>1.24164275725364</v>
+        <v>1.238390043377076</v>
       </c>
       <c r="J73" t="n">
         <v>-7</v>
@@ -3903,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>45.31999969482422</v>
+        <v>45.34999847412109</v>
       </c>
       <c r="I74" t="n">
-        <v>1.544571943322285</v>
+        <v>1.543550217315782</v>
       </c>
       <c r="J74" t="n">
         <v>-7</v>
@@ -3950,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>55.75</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="I75" t="n">
-        <v>3.946188340807175</v>
+        <v>3.949730646078899</v>
       </c>
       <c r="J75" t="n">
         <v>-7</v>
@@ -3997,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.774999618530273</v>
+        <v>8.795999526977539</v>
       </c>
       <c r="I76" t="n">
-        <v>9.800570226623458</v>
+        <v>9.77717196735129</v>
       </c>
       <c r="J76" t="n">
         <v>-7</v>
@@ -4044,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.64999961853027</v>
+        <v>11.76799964904785</v>
       </c>
       <c r="I77" t="n">
-        <v>4.806867110186634</v>
+        <v>4.758667714995298</v>
       </c>
       <c r="J77" t="n">
         <v>-7</v>
@@ -4091,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.170000076293945</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I78" t="n">
-        <v>1.843317907541938</v>
+        <v>1.826483970542351</v>
       </c>
       <c r="J78" t="n">
         <v>-7</v>
@@ -4138,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.869999885559082</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="I79" t="n">
-        <v>3.382187191325885</v>
+        <v>3.374578047405014</v>
       </c>
       <c r="J79" t="n">
         <v>-7</v>
@@ -4185,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.210000038146973</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I80" t="n">
-        <v>4.886877743701542</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J80" t="n">
         <v>-7</v>
@@ -4232,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>88</v>
+        <v>87.80000305175781</v>
       </c>
       <c r="I81" t="n">
-        <v>2.340909090909091</v>
+        <v>2.346241376307968</v>
       </c>
       <c r="J81" t="n">
         <v>-7</v>
@@ -4326,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>14.10000038146973</v>
+        <v>14.13000011444092</v>
       </c>
       <c r="I83" t="n">
-        <v>2.127659516905128</v>
+        <v>2.123142233335149</v>
       </c>
       <c r="J83" t="n">
         <v>-7</v>
@@ -4373,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>51.79999923706055</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="I84" t="n">
-        <v>1.640926665095129</v>
+        <v>1.653696448962247</v>
       </c>
       <c r="J84" t="n">
         <v>-7</v>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>35.65999984741211</v>
+        <v>35.63999938964844</v>
       </c>
       <c r="I85" t="n">
-        <v>2.383623117322267</v>
+        <v>2.384960759137613</v>
       </c>
       <c r="J85" t="n">
         <v>-7</v>
@@ -4467,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>67.05999755859375</v>
+        <v>67.04000091552734</v>
       </c>
       <c r="I86" t="n">
-        <v>1.938562551935859</v>
+        <v>1.939140784974099</v>
       </c>
       <c r="J86" t="n">
         <v>-7</v>
@@ -4514,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.039999961853027</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="I87" t="n">
-        <v>8.522727318908558</v>
+        <v>8.695652053727246</v>
       </c>
       <c r="J87" t="n">
         <v>-7</v>
@@ -4608,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.78000020980835</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I89" t="n">
-        <v>3.460207486854598</v>
+        <v>3.44827574867131</v>
       </c>
       <c r="J89" t="n">
         <v>-7</v>
@@ -4655,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.13999938964844</v>
+        <v>23.34000015258789</v>
       </c>
       <c r="I90" t="n">
-        <v>4.321521289440245</v>
+        <v>4.284490117662326</v>
       </c>
       <c r="J90" t="n">
         <v>-7</v>
@@ -4702,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.670000076293945</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I91" t="n">
-        <v>4.603854314508307</v>
+        <v>4.535865197927669</v>
       </c>
       <c r="J91" t="n">
         <v>-7</v>
@@ -4749,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>22.85000038146973</v>
+        <v>23.04000091552734</v>
       </c>
       <c r="I92" t="n">
-        <v>1.181619236290942</v>
+        <v>1.171874953433873</v>
       </c>
       <c r="J92" t="n">
         <v>-7</v>
@@ -4796,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.439999580383301</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I93" t="n">
-        <v>2.118644161972296</v>
+        <v>2.173913088547937</v>
       </c>
       <c r="J93" t="n">
         <v>-7</v>
@@ -4843,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.829999923706055</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="I94" t="n">
-        <v>2.718006818501411</v>
+        <v>2.739725955813527</v>
       </c>
       <c r="J94" t="n">
         <v>-7</v>
@@ -4890,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>21.21999931335449</v>
+        <v>21.1299991607666</v>
       </c>
       <c r="I95" t="n">
-        <v>3.722903042239145</v>
+        <v>3.738760205285965</v>
       </c>
       <c r="J95" t="n">
         <v>-7</v>
@@ -4937,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5.300000190734863</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="I96" t="n">
-        <v>1.754716917983832</v>
+        <v>1.768060759567112</v>
       </c>
       <c r="J96" t="n">
         <v>-7</v>
@@ -4984,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.949999809265137</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8633093762105317</v>
+        <v>0.8450704338862249</v>
       </c>
       <c r="J97" t="n">
         <v>-7</v>
@@ -5031,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>36.09999847412109</v>
+        <v>36.45999908447266</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9695291268527435</v>
+        <v>0.9599561403967661</v>
       </c>
       <c r="J98" t="n">
         <v>-7</v>
@@ -5078,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.855000019073486</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I99" t="n">
-        <v>8.086068540593798</v>
+        <v>8.080174769851354</v>
       </c>
       <c r="J99" t="n">
         <v>-7</v>
@@ -5125,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.279999971389771</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I100" t="n">
-        <v>2.631578980390385</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J100" t="n">
         <v>-7</v>
@@ -5172,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>13</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I101" t="n">
-        <v>1.538461538461539</v>
+        <v>1.526717512794159</v>
       </c>
       <c r="J101" t="n">
         <v>-7</v>
@@ -5219,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>7.284999847412109</v>
+        <v>7.215000152587891</v>
       </c>
       <c r="I102" t="n">
-        <v>1.41386413393803</v>
+        <v>1.427581397389933</v>
       </c>
       <c r="J102" t="n">
         <v>-7</v>
@@ -5266,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.71999979019165</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I103" t="n">
-        <v>3.321678443516761</v>
+        <v>3.310104661606765</v>
       </c>
       <c r="J103" t="n">
         <v>-7</v>
@@ -5313,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>10.23499965667725</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I104" t="n">
-        <v>4.220811084426036</v>
+        <v>4.202334739508213</v>
       </c>
       <c r="J104" t="n">
         <v>-7</v>
@@ -5360,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>25.67000007629395</v>
+        <v>25.63999938964844</v>
       </c>
       <c r="I105" t="n">
-        <v>1.714063103592807</v>
+        <v>1.716068683596147</v>
       </c>
       <c r="J105" t="n">
         <v>-7</v>
@@ -5407,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1.049999952316284</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I106" t="n">
-        <v>2.857142986894471</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J106" t="n">
         <v>-7</v>
@@ -5454,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.389999866485596</v>
+        <v>7.309999942779541</v>
       </c>
       <c r="I107" t="n">
-        <v>6.359945987705602</v>
+        <v>6.429548613940043</v>
       </c>
       <c r="J107" t="n">
         <v>-7</v>
@@ -5501,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>52.20000076293945</v>
+        <v>53.11999893188477</v>
       </c>
       <c r="I108" t="n">
-        <v>2.68199229796556</v>
+        <v>2.635542221669104</v>
       </c>
       <c r="J108" t="n">
         <v>-7</v>
@@ -5548,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.58299994468689</v>
+        <v>3.601999998092651</v>
       </c>
       <c r="I109" t="n">
-        <v>8.372872024317497</v>
+        <v>8.328706278702317</v>
       </c>
       <c r="J109" t="n">
         <v>-7</v>
@@ -5595,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>14.89999961853027</v>
+        <v>15.05000019073486</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8053691481358354</v>
+        <v>0.7973421825859831</v>
       </c>
       <c r="J110" t="n">
         <v>-7</v>
@@ -5642,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3.400000095367432</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="I111" t="n">
-        <v>4.999999859753782</v>
+        <v>5.120482030671402</v>
       </c>
       <c r="J111" t="n">
         <v>-7</v>
@@ -5689,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>23.25</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="I112" t="n">
-        <v>3.010752688172043</v>
+        <v>2.997858623400758</v>
       </c>
       <c r="J112" t="n">
         <v>-7</v>
@@ -5783,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.639999866485596</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I114" t="n">
-        <v>5.851063968298106</v>
+        <v>5.892857243211904</v>
       </c>
       <c r="J114" t="n">
         <v>-7</v>
@@ -5830,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8980000019073486</v>
+        <v>0.9029999971389771</v>
       </c>
       <c r="I115" t="n">
-        <v>7.795100206160386</v>
+        <v>7.751938009057002</v>
       </c>
       <c r="J115" t="n">
         <v>-7</v>
@@ -5877,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>51.59999847412109</v>
+        <v>51.54999923706055</v>
       </c>
       <c r="I116" t="n">
-        <v>1.37596903293725</v>
+        <v>1.377303609132866</v>
       </c>
       <c r="J116" t="n">
         <v>-7</v>
@@ -5971,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>7.28000020980835</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I118" t="n">
-        <v>1.098901067230959</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J118" t="n">
         <v>-7</v>
@@ -6065,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.206999778747559</v>
+        <v>4.217999935150146</v>
       </c>
       <c r="I120" t="n">
-        <v>4.040884453067638</v>
+        <v>4.030346197574055</v>
       </c>
       <c r="J120" t="n">
         <v>-7</v>
@@ -6159,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>56.90000152587891</v>
+        <v>57.5</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7908611387212947</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="J122" t="n">
         <v>-7</v>
@@ -6206,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.579999923706055</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7168458879374554</v>
+        <v>0.7220216656214694</v>
       </c>
       <c r="J123" t="n">
         <v>-7</v>
@@ -6253,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.04000091552734</v>
+        <v>36.88000106811523</v>
       </c>
       <c r="I124" t="n">
-        <v>2.834773148074722</v>
+        <v>2.847071501057472</v>
       </c>
       <c r="J124" t="n">
         <v>-7</v>
@@ -6347,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>20.05999946594238</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="I126" t="n">
-        <v>1.894317099285866</v>
+        <v>1.881188047760763</v>
       </c>
       <c r="J126" t="n">
         <v>-7</v>
@@ -6394,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>26.21999931335449</v>
+        <v>26.5</v>
       </c>
       <c r="I127" t="n">
-        <v>2.28832957937724</v>
+        <v>2.264150943396226</v>
       </c>
       <c r="J127" t="n">
         <v>-7</v>
@@ -6441,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>35.25</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9929078014184396</v>
+        <v>0.994318160266916</v>
       </c>
       <c r="J128" t="n">
         <v>-7</v>
@@ -6535,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2.799999952316284</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3571428632249639</v>
+        <v>0.3448275748671309</v>
       </c>
       <c r="J130" t="n">
         <v>-7</v>
@@ -6582,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21.69000053405762</v>
+        <v>21.86000061035156</v>
       </c>
       <c r="I131" t="n">
-        <v>5.163669766818941</v>
+        <v>5.123513123186449</v>
       </c>
       <c r="J131" t="n">
         <v>-7</v>
@@ -6629,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1.480000019073486</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I132" t="n">
-        <v>6.756756669679118</v>
+        <v>6.896551497342619</v>
       </c>
       <c r="J132" t="n">
         <v>-7</v>
@@ -6676,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.119999885559082</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="I133" t="n">
-        <v>2.850877228756251</v>
+        <v>2.908277541427497</v>
       </c>
       <c r="J133" t="n">
         <v>-7</v>
@@ -6723,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.21399998664856</v>
+        <v>2.196000099182129</v>
       </c>
       <c r="I134" t="n">
-        <v>4.168925047724099</v>
+        <v>4.20309634932967</v>
       </c>
       <c r="J134" t="n">
         <v>-7</v>
@@ -6817,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>5.300000190734863</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="I136" t="n">
-        <v>1.811320689531697</v>
+        <v>1.794392555350768</v>
       </c>
       <c r="J136" t="n">
         <v>-14</v>
@@ -6864,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.25</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I137" t="n">
-        <v>4.8</v>
+        <v>4.761904617736313</v>
       </c>
       <c r="J137" t="n">
         <v>-14</v>
@@ -6958,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8.899999618530273</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I139" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J139" t="n">
         <v>-14</v>
@@ -7052,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>2.220000028610229</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I141" t="n">
-        <v>2.702702667871647</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J141" t="n">
         <v>-14</v>
@@ -7099,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.39999961853027</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="I142" t="n">
-        <v>3.246753327177799</v>
+        <v>3.234152644025023</v>
       </c>
       <c r="J142" t="n">
         <v>-14</v>
@@ -7146,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.680000066757202</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="I143" t="n">
-        <v>2.71739125505287</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J143" t="n">
         <v>-14</v>
@@ -7193,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.049999952316284</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="I144" t="n">
-        <v>3.606557433434118</v>
+        <v>3.571428659895579</v>
       </c>
       <c r="J144" t="n">
         <v>-14</v>
@@ -7475,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>7.269999980926514</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="I150" t="n">
-        <v>3.026134808489538</v>
+        <v>3.04287689377064</v>
       </c>
       <c r="J150" t="n">
         <v>-14</v>
@@ -7522,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>25.14999961853027</v>
+        <v>25.64999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>2.425447352892037</v>
+        <v>2.378167676693917</v>
       </c>
       <c r="J151" t="n">
         <v>-21</v>
@@ -7569,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2.859999895095825</v>
+        <v>2.880000114440918</v>
       </c>
       <c r="I152" t="n">
-        <v>5.244755437131728</v>
+        <v>5.208333126372769</v>
       </c>
       <c r="J152" t="n">
         <v>-21</v>
@@ -7616,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.69999980926514</v>
+        <v>11.5</v>
       </c>
       <c r="I153" t="n">
-        <v>5.982906080440066</v>
+        <v>6.08695652173913</v>
       </c>
       <c r="J153" t="n">
         <v>-21</v>
@@ -7663,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>9.130000114440918</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I154" t="n">
-        <v>5.591456665948364</v>
+        <v>5.622246743275703</v>
       </c>
       <c r="J154" t="n">
         <v>-21</v>
@@ -7710,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.020000457763672</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I155" t="n">
-        <v>3.366583348990081</v>
+        <v>3.349875756121116</v>
       </c>
       <c r="J155" t="n">
         <v>-21</v>
@@ -7757,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.739999771118164</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="I156" t="n">
-        <v>5.192878514622488</v>
+        <v>5.247376251822633</v>
       </c>
       <c r="J156" t="n">
         <v>-21</v>
@@ -7851,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>17.10000038146973</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="I158" t="n">
-        <v>4.385964814437848</v>
+        <v>4.322766475561698</v>
       </c>
       <c r="J158" t="n">
         <v>-21</v>
@@ -7898,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.69999980926514</v>
+        <v>10.89999961853027</v>
       </c>
       <c r="I159" t="n">
-        <v>4.01869166042099</v>
+        <v>3.94495426650281</v>
       </c>
       <c r="J159" t="n">
         <v>-21</v>
@@ -7945,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>4.46999979019165</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="I160" t="n">
-        <v>3.355704855493265</v>
+        <v>3.363228670785428</v>
       </c>
       <c r="J160" t="n">
         <v>-21</v>
@@ -7992,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.18000030517578</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I161" t="n">
-        <v>1.618793062888634</v>
+        <v>1.616139369529026</v>
       </c>
       <c r="J161" t="n">
         <v>-21</v>
@@ -8039,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>29.39999961853027</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I162" t="n">
-        <v>3.741496647185977</v>
+        <v>3.75426630936102</v>
       </c>
       <c r="J162" t="n">
         <v>-21</v>
@@ -8086,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>66</v>
+        <v>65.90000152587891</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7121212121212122</v>
+        <v>0.7132018044270168</v>
       </c>
       <c r="J163" t="n">
         <v>-21</v>
@@ -8133,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>85.5</v>
+        <v>84.90000152587891</v>
       </c>
       <c r="I164" t="n">
-        <v>1.403508771929824</v>
+        <v>1.413427536434402</v>
       </c>
       <c r="J164" t="n">
         <v>-21</v>
@@ -8180,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.89999961853027</v>
+        <v>23.75</v>
       </c>
       <c r="I165" t="n">
-        <v>1.179039320950559</v>
+        <v>1.136842105263158</v>
       </c>
       <c r="J165" t="n">
         <v>-21</v>
@@ -8274,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>34.15000152587891</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8784772667511</v>
+        <v>0.8720929845724334</v>
       </c>
       <c r="J167" t="n">
         <v>-21</v>
@@ -8321,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0.1759999990463257</v>
+        <v>0.1738000065088272</v>
       </c>
       <c r="I168" t="n">
-        <v>3.977272748823994</v>
+        <v>4.027617800833899</v>
       </c>
       <c r="J168" t="n">
         <v>-28</v>
@@ -8368,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.820000171661377</v>
+        <v>6.809999942779541</v>
       </c>
       <c r="I169" t="n">
-        <v>2.346040996667943</v>
+        <v>2.34948606966794</v>
       </c>
       <c r="J169" t="n">
         <v>-28</v>
@@ -8462,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>8.350000381469727</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="I171" t="n">
-        <v>2.994011839266482</v>
+        <v>2.910360833051709</v>
       </c>
       <c r="J171" t="n">
         <v>-28</v>
@@ -10293,163 +10297,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DIADEMA CAPITAL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rocket Sharing Company S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Telesia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>